--- a/15-CONTAS-A-PAGAR-2026-08-31.xlsx
+++ b/15-CONTAS-A-PAGAR-2026-08-31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre\Documents\Gemini-Cli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{82F6D6FE-3CC4-42FD-A904-4AFF6D460954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0413DD-AEB5-46E9-A926-68E64B6DB831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC821CCE-D1CC-4DCD-95CD-22E0F2F59A65}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="195">
   <si>
     <t>Dt.Ref: 31/08/2026</t>
   </si>
@@ -618,16 +618,13 @@
   </si>
   <si>
     <t>PR - VENCE 10.07  ** DAMSP/GSI 14.061.778/0001-15/ RECEITA:TFE /CCM 4.341.913-5/INCIDENCIA:06/2025/VENC 10.07.2025 COD BOL=818500000020266857012504710100014641767000299478</t>
-  </si>
-  <si>
-    <t>SEM PA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Courier New"/>
@@ -743,13 +740,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -929,6 +921,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -1099,19 +1097,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1120,10 +1118,25 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1510,7 +1523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2B4AC10-3051-437A-A7CF-3BB0896D76E6}">
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -1679,7 +1692,7 @@
       <c r="C5" s="3">
         <v>46148</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>240</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1789,7 +1802,7 @@
       <c r="C6" s="3">
         <v>46162</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>291971.90999999997</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1899,7 +1912,7 @@
       <c r="C7" s="3">
         <v>46197</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>14851</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -1999,113 +2012,113 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="9">
         <v>46259</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="10">
         <v>2106.65</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="J8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="9">
         <v>46259</v>
       </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
         <v>46259</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="O8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="Q8" s="11">
         <v>2106.65</v>
       </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5">
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>0</v>
+      </c>
+      <c r="T8" s="11">
+        <v>0</v>
+      </c>
+      <c r="U8" s="12">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="W8" s="4">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB8" s="2" t="s">
+      <c r="V8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="W8" s="11">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF8" s="2" t="s">
+      <c r="AC8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AG8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ8" s="2" t="s">
+      <c r="AG8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ8" s="8" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2119,7 +2132,7 @@
       <c r="C9" s="3">
         <v>46266</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>8706.1299999999992</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -2339,7 +2352,7 @@
       <c r="C11" s="3">
         <v>46269</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>160.94</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -2449,7 +2462,7 @@
       <c r="C12" s="3">
         <v>46270</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <v>4619.1000000000004</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -2559,7 +2572,7 @@
       <c r="C13" s="3">
         <v>46271</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>1798.4</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -2669,7 +2682,7 @@
       <c r="C14" s="3">
         <v>46275</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>672</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -2779,7 +2792,7 @@
       <c r="C15" s="3">
         <v>46275</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <v>99</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -2889,7 +2902,7 @@
       <c r="C16" s="3">
         <v>46275</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>6000</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -3109,7 +3122,7 @@
       <c r="C18" s="3">
         <v>46275</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="6">
         <v>1176</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -3219,7 +3232,7 @@
       <c r="C19" s="3">
         <v>46275</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="6">
         <v>650</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -3329,7 +3342,7 @@
       <c r="C20" s="3">
         <v>46275</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="6">
         <v>513.53</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -3439,7 +3452,7 @@
       <c r="C21" s="3">
         <v>46275</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="6">
         <v>447.8</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -3549,7 +3562,7 @@
       <c r="C22" s="3">
         <v>46275</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="6">
         <v>500</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -3659,7 +3672,7 @@
       <c r="C23" s="3">
         <v>46276</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="6">
         <v>3414.76</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -3879,7 +3892,7 @@
       <c r="C25" s="3">
         <v>46276</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>4730.3900000000003</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -3989,7 +4002,7 @@
       <c r="C26" s="3">
         <v>46277</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="6">
         <v>4619.1000000000004</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -4099,7 +4112,7 @@
       <c r="C27" s="3">
         <v>46280</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="6">
         <v>270.02999999999997</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -4209,7 +4222,7 @@
       <c r="C28" s="3">
         <v>46280</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="6">
         <v>90</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -4319,7 +4332,7 @@
       <c r="C29" s="3">
         <v>46280</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="6">
         <v>5852.25</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -4429,7 +4442,7 @@
       <c r="C30" s="3">
         <v>46280</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="6">
         <v>199.99</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -4649,7 +4662,7 @@
       <c r="C32" s="3">
         <v>46280</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="6">
         <v>129.99</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -4759,7 +4772,7 @@
       <c r="C33" s="3">
         <v>46280</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="6">
         <v>89.9</v>
       </c>
       <c r="E33" s="2" t="s">
@@ -4869,7 +4882,7 @@
       <c r="C34" s="3">
         <v>46282</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="6">
         <v>513.53</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -4979,7 +4992,7 @@
       <c r="C35" s="3">
         <v>46283</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="6">
         <v>1400</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -5089,7 +5102,7 @@
       <c r="C36" s="3">
         <v>46284</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="6">
         <v>4619.1000000000004</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -5199,7 +5212,7 @@
       <c r="C37" s="3">
         <v>46285</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="6">
         <v>1530</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -5419,7 +5432,7 @@
       <c r="C39" s="3">
         <v>46285</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="6">
         <v>499.8</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -5529,7 +5542,7 @@
       <c r="C40" s="3">
         <v>46285</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="6">
         <v>269.89999999999998</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -5639,7 +5652,7 @@
       <c r="C41" s="3">
         <v>46285</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="6">
         <v>9000</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -5749,7 +5762,7 @@
       <c r="C42" s="3">
         <v>46285</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="6">
         <v>5959</v>
       </c>
       <c r="E42" s="2" t="s">
@@ -5859,7 +5872,7 @@
       <c r="C43" s="3">
         <v>46285</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="6">
         <v>71.55</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -5969,7 +5982,7 @@
       <c r="C44" s="3">
         <v>46285</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="6">
         <v>18753.650000000001</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -6189,7 +6202,7 @@
       <c r="C46" s="3">
         <v>46287</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="6">
         <v>5852.25</v>
       </c>
       <c r="E46" s="2" t="s">
@@ -6299,7 +6312,7 @@
       <c r="C47" s="3">
         <v>46288</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="6">
         <v>2500</v>
       </c>
       <c r="E47" s="2" t="s">
@@ -6409,7 +6422,7 @@
       <c r="C48" s="3">
         <v>46289</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="6">
         <v>513.54</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -6519,7 +6532,7 @@
       <c r="C49" s="3">
         <v>46289</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="6">
         <v>833.37</v>
       </c>
       <c r="E49" s="2" t="s">
@@ -6629,7 +6642,7 @@
       <c r="C50" s="3">
         <v>46290</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="6">
         <v>626.41999999999996</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -6739,7 +6752,7 @@
       <c r="C51" s="3">
         <v>46290</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="6">
         <v>1000</v>
       </c>
       <c r="E51" s="2" t="s">
@@ -6959,7 +6972,7 @@
       <c r="C53" s="3">
         <v>46294</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="6">
         <v>5852.25</v>
       </c>
       <c r="E53" s="2" t="s">
@@ -7069,7 +7082,7 @@
       <c r="C54" s="3">
         <v>46295</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="6">
         <v>4619.08</v>
       </c>
       <c r="E54" s="2" t="s">
@@ -7179,7 +7192,7 @@
       <c r="C55" s="3">
         <v>46295</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="6">
         <v>139.80000000000001</v>
       </c>
       <c r="E55" s="2" t="s">
@@ -7289,7 +7302,7 @@
       <c r="C56" s="3">
         <v>46308</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="6">
         <v>5852.25</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -7399,7 +7412,7 @@
       <c r="C57" s="3">
         <v>46325</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="6">
         <v>0.01</v>
       </c>
       <c r="E57" s="2" t="s">
@@ -7619,7 +7632,7 @@
       <c r="C59" s="3">
         <v>46420</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="6">
         <v>76</v>
       </c>
       <c r="E59" s="2" t="s">
@@ -7729,7 +7742,7 @@
       <c r="C60" s="3">
         <v>46577</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="6">
         <v>248</v>
       </c>
       <c r="E60" s="2" t="s">
@@ -7830,19 +7843,19 @@
       </c>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="D63" s="6">
-        <f>SUM(D5:D60)</f>
-        <v>424638.37000000005</v>
+      <c r="Q63" s="6">
+        <f>SUM(Q5:Q60)</f>
+        <v>207681.05999999994</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="C64" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D64" s="6">
-        <f>D63-D8</f>
-        <v>422531.72000000003</v>
-      </c>
+      <c r="Q64" s="6">
+        <f>Q63-Q8</f>
+        <v>205574.40999999995</v>
+      </c>
+    </row>
+    <row r="65" spans="17:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
